--- a/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0001T0006Z000C1N6_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0001T0006Z000C1N6_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>42.85336700043084</v>
+        <v>6.963672137570011</v>
       </c>
       <c r="D2" t="n">
-        <v>42.14437788804686</v>
+        <v>6.848461406807616</v>
       </c>
       <c r="E2" t="n">
-        <v>11.33360341368107</v>
+        <v>1.841710554723174</v>
       </c>
       <c r="F2" t="n">
-        <v>11.09524104094846</v>
+        <v>1.802976669154124</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>47.71594452862121</v>
+        <v>7.753840985900946</v>
       </c>
       <c r="D3" t="n">
-        <v>48.32340667714527</v>
+        <v>7.852553585036107</v>
       </c>
       <c r="E3" t="n">
-        <v>11.33360341368107</v>
+        <v>1.841710554723174</v>
       </c>
       <c r="F3" t="n">
-        <v>11.09524104094846</v>
+        <v>1.802976669154124</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>47.77991886689853</v>
+        <v>7.764236815871012</v>
       </c>
       <c r="D4" t="n">
-        <v>47.02266820316346</v>
+        <v>7.641183583014063</v>
       </c>
       <c r="E4" t="n">
-        <v>11.33360341368107</v>
+        <v>1.841710554723174</v>
       </c>
       <c r="F4" t="n">
-        <v>11.09524104094846</v>
+        <v>1.802976669154124</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>32.75384622449162</v>
+        <v>5.322500011479888</v>
       </c>
       <c r="D5" t="n">
-        <v>32.01349725248778</v>
+        <v>5.202193303529264</v>
       </c>
       <c r="E5" t="n">
-        <v>11.33360341368107</v>
+        <v>1.841710554723174</v>
       </c>
       <c r="F5" t="n">
-        <v>11.09524104094846</v>
+        <v>1.802976669154124</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>47.47936893205247</v>
+        <v>7.715397451458526</v>
       </c>
       <c r="D6" t="n">
-        <v>48.21314203322203</v>
+        <v>7.834635580398579</v>
       </c>
       <c r="E6" t="n">
-        <v>11.33360341368107</v>
+        <v>1.841710554723174</v>
       </c>
       <c r="F6" t="n">
-        <v>11.09524104094846</v>
+        <v>1.802976669154124</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>54.98431656164035</v>
+        <v>8.934951441266557</v>
       </c>
       <c r="D7" t="n">
-        <v>50.20209158989294</v>
+        <v>8.157839883357603</v>
       </c>
       <c r="E7" t="n">
-        <v>11.33360341368107</v>
+        <v>1.841710554723174</v>
       </c>
       <c r="F7" t="n">
-        <v>11.09524104094846</v>
+        <v>1.802976669154124</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>42.86091709247185</v>
+        <v>6.964899027526676</v>
       </c>
       <c r="D8" t="n">
-        <v>43.25808963997681</v>
+        <v>7.029439566496232</v>
       </c>
       <c r="E8" t="n">
-        <v>11.33360341368107</v>
+        <v>1.841710554723174</v>
       </c>
       <c r="F8" t="n">
-        <v>11.09524104094846</v>
+        <v>1.802976669154124</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>17.32532177205131</v>
+        <v>2.815364787958339</v>
       </c>
       <c r="D9" t="n">
-        <v>18.07716481995228</v>
+        <v>2.937539283242245</v>
       </c>
       <c r="E9" t="n">
-        <v>11.33360341368107</v>
+        <v>1.841710554723174</v>
       </c>
       <c r="F9" t="n">
-        <v>11.09524104094846</v>
+        <v>1.802976669154124</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>42.26848307245734</v>
+        <v>6.868628499274318</v>
       </c>
       <c r="D10" t="n">
-        <v>42.39035857361907</v>
+        <v>6.8884332682131</v>
       </c>
       <c r="E10" t="n">
-        <v>11.33360341368107</v>
+        <v>1.841710554723174</v>
       </c>
       <c r="F10" t="n">
-        <v>11.09524104094846</v>
+        <v>1.802976669154124</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>34.47502139623706</v>
+        <v>5.602190976888522</v>
       </c>
       <c r="D11" t="n">
-        <v>34.01532742749951</v>
+        <v>5.527490706968671</v>
       </c>
       <c r="E11" t="n">
-        <v>11.33360341368107</v>
+        <v>1.841710554723174</v>
       </c>
       <c r="F11" t="n">
-        <v>11.09524104094846</v>
+        <v>1.802976669154124</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>19.94813464245533</v>
+        <v>3.24157187939899</v>
       </c>
       <c r="D12" t="n">
-        <v>17.92344832893492</v>
+        <v>2.912560353451925</v>
       </c>
       <c r="E12" t="n">
-        <v>11.33360341368107</v>
+        <v>1.841710554723174</v>
       </c>
       <c r="F12" t="n">
-        <v>11.09524104094846</v>
+        <v>1.802976669154124</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
